--- a/StructureDefinition-anonymous.xlsx
+++ b/StructureDefinition-anonymous.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-04-21T10:41:40+00:00</t>
+    <t>2022-05-02T16:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anonymous.xlsx
+++ b/StructureDefinition-anonymous.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-02T16:42:45+00:00</t>
+    <t>2022-05-02T16:43:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
